--- a/daily_matches/job_matches_2026-09-28.xlsx
+++ b/daily_matches/job_matches_2026-09-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,122 +468,122 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - West Region</t>
+          <t>Sr AI/ML Engineer Remote Nationwide or Office-Based in MN/DC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Dataflow, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a19bfa35530d300</t>
+          <t>https://www.indeed.com/viewjob?jk=cc107e981cfd30ac</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - East Region</t>
+          <t>Sr. AI/ML Engineer - OptumHealth - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Dataflow, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f180772fc14dcad</t>
+          <t>https://www.indeed.com/viewjob?jk=bf3a051000d27864</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Architect - Intelligence Engineering (West)</t>
+          <t>Software Engineer || - Authentication</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, GCP Vertex AI, FastAPI, CI/CD, Git, Databricks, Python</t>
+          <t>RAG, S3, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bbe64a1948c26b</t>
+          <t>https://www.indeed.com/viewjob?jk=309ab450891b7cb4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Architect - Intelligence Engineering (Central)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,77 +591,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, GCP Vertex AI, FastAPI, CI/CD, Git, Databricks, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419bca6d3e7f6a90</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec4e5367dc5fdcc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Consultant/Senior Consultant - (US-CENTRAL)</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Cortex, CI/CD, Git, Snowflake, Databricks, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df197bbb6fa7ca32</t>
+          <t>https://www.indeed.com/viewjob?jk=20435d9ad597a311</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full-stack Engineer 4 (DevOps) - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DelRicht Research</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, BigQuery, Docker, CI/CD, Terraform, BigQuery, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fd99bddc112896</t>
+          <t>https://www.indeed.com/viewjob?jk=5197f016f75b35ad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DelRicht Research</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, BigQuery, Docker, CI/CD, Terraform, BigQuery, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=207397b9c16660b8</t>
+          <t>https://www.indeed.com/viewjob?jk=04d0e6836ba7d269</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer with ETL/ELT pipelines and API integrations</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DHANU GLOBAL ENTERPRISES, INC.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Glue, CI/CD, Git, PySpark, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8385d0cbea264ab</t>
+          <t>https://www.indeed.com/viewjob?jk=997a5797f758baff</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Architect - AI Accelerated Development - Cloud Build Practice</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37602d170cbc74b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f890393388599b0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer (SWIFT), Global Banking &amp; Markets, Transaction Banking</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, EC2, Terraform, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,812 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdc55cfac74d874</t>
+          <t>https://www.indeed.com/viewjob?jk=9e70c9dd57a7289c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data Scientist - BlackLocus</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2ba786a466821b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Python, Angular)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c43596c71eebc7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82382cea5259933b</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Velir</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fff8cf7c0caa031</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Velir</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b433e5c3de97183c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Velir</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2abd9312c38916a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Velir</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54c9fe751059a090</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Velir</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=519ba6eb81f01ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Velir</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02e9b1f872b9ca87</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Terraform, Git, BigQuery, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efab3b52406bee28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9fadd67c5d6b60a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, AKS, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3d60c1504af0532</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Advanced Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, R, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=184df85b2572f6da</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>West Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10a2848f3bd89c2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea78b0860a28a7b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Native Founding Product and Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SGS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hayward, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae0b0b80f557bd14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Native Founding Product and Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SGS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8372fea10d24e8e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Native Founding Product and Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SGS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bloomfield, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6755de8fbb5220e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer (Hybrid, NYC)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Git, Kafka, Cassandra, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f96c1c8e52a0ebf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Northwestern Medicine</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0cb7f01b2f338d5</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20000dac4b171f7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Production Cloud and Container Services</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fastly</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce22089613d67546</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI/ML engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MAMSYS Consulting Services Ltd</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fff4abb3faf8cbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e3889fc78d978d5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-28.xlsx
+++ b/daily_matches/job_matches_2026-09-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer Remote Nationwide or Office-Based in MN/DC</t>
+          <t>Jr. AI Developer(Korean Bilingual)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc107e981cfd30ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1b0fd31b40f822</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - OptumHealth - Remote</t>
+          <t>Salesforce Developer with python</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>LangChain, RAG, LLaMA, Redshift, BigQuery, FastAPI, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf3a051000d27864</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f22a963618e371</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer || - Authentication</t>
+          <t>Salesforce Developer with python</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, MySQL</t>
+          <t>LangChain, RAG, LLaMA, Redshift, BigQuery, FastAPI, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=309ab450891b7cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=fae70768d6fa1ea0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Kubernetes, CI/CD, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,119 +601,119 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec4e5367dc5fdcc</t>
+          <t>https://www.indeed.com/viewjob?jk=85c0bbc23bb8dc35</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Gen AI Engineer with Java &amp; Microservices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>American IT Systems</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20435d9ad597a311</t>
+          <t>https://www.indeed.com/viewjob?jk=5b379a101d7ec8d1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (DevOps) - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Sr. Azure DevOps and SRE Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Berlin Packaging</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5197f016f75b35ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9b4b58bac9acaa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, Gemini, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d0e6836ba7d269</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ae5f57c116bd7e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,42 +723,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997a5797f758baff</t>
+          <t>https://www.indeed.com/viewjob?jk=271619709a30cff7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Taskrabbit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f890393388599b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7814dca29175e0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e70c9dd57a7289c</t>
+          <t>https://www.indeed.com/viewjob?jk=99a8ea27729acb82</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,112 +836,112 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ba786a466821b0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2f25853b8a0412</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Python, Angular)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Anytime Fitness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c43596c71eebc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4491c69c48afea0f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82382cea5259933b</t>
+          <t>https://www.indeed.com/viewjob?jk=fff4a69ead6f5698</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff8cf7c0caa031</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7b78785afe8fda</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b433e5c3de97183c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d038dc3b36855c8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+          <t>Apache Airflow, Hadoop, MongoDB, Cassandra, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2abd9312c38916a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e0f177f03aebbc1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+          <t>Apache Airflow, Hadoop, MongoDB, Cassandra, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c9fe751059a090</t>
+          <t>https://www.indeed.com/viewjob?jk=e78ec447c6921557</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+          <t>Apache Airflow, Hadoop, MongoDB, Cassandra, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519ba6eb81f01ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=34d121867f08ee42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+          <t>Apache Airflow, Hadoop, MongoDB, Cassandra, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e9b1f872b9ca87</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd3cf170c956d7d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Terraform, Git, BigQuery, Python, SQL, R, Java, Scala</t>
+          <t>Apache Airflow, Hadoop, MongoDB, Cassandra, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efab3b52406bee28</t>
+          <t>https://www.indeed.com/viewjob?jk=12c8ce709821c415</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>Apache Airflow, Hadoop, MongoDB, Cassandra, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fadd67c5d6b60a</t>
+          <t>https://www.indeed.com/viewjob?jk=1850028e14e4bff5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Creative Systems Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HH Global</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, AKS, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL</t>
+          <t>Generative AI, Gemini, Prompt Engineering, Kubernetes, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d60c1504af0532</t>
+          <t>https://www.indeed.com/viewjob?jk=6ada2aa7bc56b244</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Advanced Data Scientist</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, R, Optimization, Hypothesis Testing</t>
+          <t>RAG, Gemini, EC2, Docker, CI/CD, Jenkins, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184df85b2572f6da</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5357a06361740b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>West Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, CI/CD, Git, Python, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a2848f3bd89c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=636a884296b1a8f9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Senior NLP / Machine Learning Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>RedBalloon LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, CI/CD, Git, Python, R, Scala</t>
+          <t>Hugging Face, Sentence Transformers, PyTorch, MLflow, Docker, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea78b0860a28a7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=42a927dd37c52c0b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Native Founding Product and Platform Engineer</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SGS</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, S3, EC2, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0b0b80f557bd14</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11d23fd998ecc0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Native Founding Product and Platform Engineer</t>
+          <t>AI Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SGS</t>
+          <t>Planet DDS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, PyTorch, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8372fea10d24e8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0ba664416511b9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Native Founding Product and Platform Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SGS</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bloomfield, NJ, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6755de8fbb5220e3</t>
+          <t>https://www.indeed.com/viewjob?jk=4f966e76c6499fe1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer (Hybrid, NYC)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Kafka, Cassandra, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f96c1c8e52a0ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=17e18497d5c7efef</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI-Native Application Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Northwestern Medicine</t>
+          <t>One Park Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Git, MongoDB, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,112 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20000dac4b171f7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Production Cloud and Container Services</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Fastly</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22089613d67546</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AI/ML engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>MAMSYS Consulting Services Ltd</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Baton Rouge, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff4abb3faf8cbe</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>TEEMA</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3889fc78d978d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1470bca8921fd4</t>
         </is>
       </c>
     </row>
